--- a/sample_data/test_report.xlsx
+++ b/sample_data/test_report.xlsx
@@ -11,7 +11,9 @@
     <sheet name="Top Products" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Top Regions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Anomalies" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Raw Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Data Quality" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Revenue Trend" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Raw Data" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -808,6 +810,306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data Quality Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Rows with missing values</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate rows</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Invalid date rows</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Missing Values by Column</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Current Period</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Previous Period</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Current Value</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>19097.81</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Previous Value</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11782.07</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Growth %</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>62.09</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Growth %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1311.45</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3901.77</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-66.39</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8025.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4664.16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>72.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2587.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1052.36</v>
+      </c>
+      <c r="D13" t="n">
+        <v>145.89</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4520.07</v>
+      </c>
+      <c r="C14" t="n">
+        <v>763.04</v>
+      </c>
+      <c r="D14" t="n">
+        <v>492.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2557.64</v>
+      </c>
+      <c r="C15" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="D15" t="n">
+        <v>593.62</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Insights</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>South down 66.39% MoM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>East up 593.62% MoM.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
